--- a/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
@@ -615,14 +615,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Best for Former Dog Owners — Ranked Product List</t>
+          <t>Best For Former Dog Owners — Ranked Product List</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-28  |  Products shown: 6  |  Eliminated by dedup rule: 4  |  Pre-filter: Category equal Dog  (19 products removed)</t>
+          <t>Generated: 2026-07-02  |  Products shown: 6  |  Eliminated by dedup rule: 4  |  Pre-filter: Category equal Dog  (19 products removed)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>5</v>
@@ -816,14 +816,14 @@
         <v>4</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>5</v>
       </c>
       <c r="Q6" s="8" t="inlineStr">
         <is>
-          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22).</t>
+          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
         <v>5164</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="J7" s="13" t="n">
         <v>5</v>
@@ -879,14 +879,14 @@
         <v>3</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" s="13" t="n">
         <v>5</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Q10" s="8" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22).</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22).</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>Eliminated by dedup rule — Best for Former Dog Owners  (same Manufacturer x Price Category x Animal Category as a higher-scoring product)</t>
+          <t>Eliminated by dedup rule — Best For Former Dog Owners  (same Manufacturer x Price Category x Animal Category as a higher-scoring product)</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="E3" s="18" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>4.3</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
-          <t>score=4.25 rating=4.3</t>
+          <t>score=4.10 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>Weights applied — Best for Former Dog Owners</t>
+          <t>Weights applied — Best For Former Dog Owners</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Whether sounds are soothing, realistic, or annoying. Absence of sound = 2 (neutral — not obnoxious, but not soothing either).</t>
+          <t>Whether sounds are soothing, realistic, or unsettling — including verified reports in retailer reviews (Amazon, Best Buy, Walmart) of a product startling users or being unsuitable for noise-sensitive/quiet environments. As of 2026-07, this feature absorbs the former 'Noise sensitivity fit' feature (eliminated as a separate row — overlapping scope). Products that produce no sound of any kind are scored N/A, not on the 1-5 scale.</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>1 – 5</t>
+          <t>1 - 5, or N/A if the product produces no sound of any kind</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-02  |  Products shown: 6  |  Eliminated by dedup rule: 4  |  Pre-filter: Category equal Dog  (19 products removed)</t>
+          <t>Generated: 2026-07-07  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -918,10 +918,10 @@
         <v>44.45</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>2.8</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
@@ -1288,88 +1288,12 @@
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
           <t>score=2.80 rating=4.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Perfect Petzzz</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Original Border Collie</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Budget Friendly</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>Original Beagle</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>score=2.80 rating=4.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>Perfect Petzzz</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Original Shih Tzu</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>Budget Friendly</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>Original Beagle</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>score=2.80 rating=4.2</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-07  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
+          <t>Generated: 2026-07-08  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
+          <t>Generated: 2026-07-11  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
         </is>
       </c>
     </row>
